--- a/output/pdf_financials_xlsx/KOVO.xlsx
+++ b/output/pdf_financials_xlsx/KOVO.xlsx
@@ -1257,22 +1257,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.305</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="35">
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.305</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="37">
@@ -1607,22 +1607,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.362</v>
+        <v>0.209</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.043</v>
+        <v>0.332</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.912</v>
+        <v>0.22</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.418</v>
+        <v>0.316</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.719</v>
+        <v>0.414</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.468</v>
+        <v>0.257</v>
       </c>
     </row>
     <row r="49">
@@ -3537,22 +3537,22 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.114</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.131</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.255</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.188</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.172</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="125">
@@ -3562,22 +3562,22 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.114</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.131</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.255</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.188</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.172</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="126">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -8002,7 +8002,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>-0.114</v>
       </c>
@@ -9476,7 +9480,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -10566,7 +10574,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -13534,7 +13546,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -14588,7 +14600,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -15394,7 +15406,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E260" s="5" t="n">

--- a/output/pdf_financials_xlsx/KOVO.xlsx
+++ b/output/pdf_financials_xlsx/KOVO.xlsx
@@ -7596,7 +7596,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -8450,7 +8454,11 @@
           <t>Additions to intangible assets 4</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -9042,7 +9050,11 @@
           <t>Additions to intangible assets 6</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -9710,7 +9722,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KOVO.xlsx
+++ b/output/pdf_financials_xlsx/KOVO.xlsx
@@ -7388,7 +7388,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -8928,7 +8932,11 @@
           <t>Deferred tax recovery 12</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
